--- a/processed_ruby_restored_xlsx/sc235_凛７：天体観測.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc235_凛７：天体観測.ss.xlsx
@@ -499,9 +499,9 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>Since everyone’s fallen asleep, there’s nothing for me
-to do either, and I want to be awake before everyone
-else wakes up.</t>
+          <t>Since everyone’s fallen asleep, there’s nothing for
+me to do either, and I want to be awake before
+everyone else wakes up.</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -531,8 +531,8 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>Judging that way, I spread out her futon in the corner
-of the Assembly Hall and lay down….</t>
+          <t>Judging that way, I spread out her futon in the
+corner of the Assembly Hall and lay down….</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1020,7 +1020,8 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan, wearing a mischievous smile beyond my penis.</t>
+          <t>Rin-chan, wearing a mischievous smile beyond my
+penis.</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1384,7 +1385,8 @@
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>「Ugh, guu... Rin-chan made it come out, didn't you...」</t>
+          <t>「Ugh, guu... Rin-chan made it come out, didn't
+you...」</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1460,8 +1462,8 @@
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>「You're all twitchy already... Rin loves your hands so
-much, right... ？」</t>
+          <t>「You're all twitchy already... Rin loves your hands
+so much, right... ？」</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1492,8 +1494,8 @@
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>I'm not just applying force; I'm skillfully adjusting,
-repeating squeezes and releases.</t>
+          <t>I'm not just applying force; I'm skillfully
+adjusting, repeating squeezes and releases.</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1829,9 +1831,9 @@
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>Holding my penis, she gradually increased the pressure
-from my pinky to my ring finger, then to my middle and
-index….</t>
+          <t>Holding my penis, she gradually increased the
+pressure from my pinky to my ring finger, then to my
+middle and index….</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1936,9 +1938,9 @@
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan's handjob tends to get heavy-handed, but when
-she's drunk it's totally different — she adjusts the
-pressure just right.”</t>
+          <t>Rin-chan's handjob tends to get heavy-handed, but
+when she's drunk it's totally different — she adjusts
+the pressure just right.”</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -2453,8 +2455,8 @@
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>A thick, drippy strand of saliva drops onto the glans,
-and the sensation surges all at once.</t>
+          <t>A thick, drippy strand of saliva drops onto the
+glans, and the sensation surges all at once.</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2516,8 +2518,8 @@
       <c r="B135" s="1" t="inlineStr">
         <is>
           <t>A jolting, tingling sensation ran through the glans
-and up into my head, and I couldn't help but let out a
-loud noise.</t>
+and up into my head, and I couldn't help but let out
+a loud noise.</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2668,8 +2670,8 @@
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>Meanwhile, the glans is being coated in hot saliva and
-rubbed.</t>
+          <t>Meanwhile, the glans is being coated in hot saliva
+and rubbed.</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2761,8 +2763,8 @@
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan’s little hands, suddenly unlike a moment ago,
-keep attacking only the glans.</t>
+          <t>Rin-chan’s little hands, suddenly unlike a moment
+ago, keep attacking only the glans.</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -3114,7 +3116,8 @@
       </c>
       <c r="B174" s="1" t="inlineStr">
         <is>
-          <t>「Y-yeah...！ I'll be good... please let me cum... ggh！」</t>
+          <t>「Y-yeah...！ I'll be good... please let me cum...
+ggh！」</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -3358,8 +3361,8 @@
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>Having been made to hold back earlier, it felt so good
-I was on the verge of cumming right away.</t>
+          <t>Having been made to hold back earlier, it felt so
+good I was on the verge of cumming right away.</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3450,8 +3453,8 @@
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t>Her breaths grow ragged, and her voice starts to break
-off.</t>
+          <t>Her breaths grow ragged, and her voice starts to
+break off.</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -3466,8 +3469,8 @@
       </c>
       <c r="B197" s="1" t="inlineStr">
         <is>
-          <t>Even before that, the penis had already filled and was
-dripping its holding juices.</t>
+          <t>Even before that, the penis had already filled and
+was dripping its holding juices.</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -3618,8 +3621,8 @@
       </c>
       <c r="B207" s="1" t="inlineStr">
         <is>
-          <t>My mind has gone completely blank, and I'm being toyed
-with by Rin-chan….</t>
+          <t>My mind has gone completely blank, and I'm being
+toyed with by Rin-chan….</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3665,7 +3668,8 @@
       </c>
       <c r="B210" s="1" t="inlineStr">
         <is>
-          <t>「Heh… if I spread it open here, a lot might come out…」</t>
+          <t>「Heh… if I spread it open here, a lot might come
+out…」</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -3833,8 +3837,8 @@
       </c>
       <c r="B221" s="1" t="inlineStr">
         <is>
-          <t>She's drunk, so her words and actions are all over the
-place.</t>
+          <t>She's drunk, so her words and actions are all over
+the place.</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -3986,9 +3990,9 @@
       </c>
       <c r="B231" s="1" t="inlineStr">
         <is>
-          <t>Even when they try to hold back their voice as they're
-being provoked, the sobs welling up from the back of
-their throat can't be stopped.</t>
+          <t>Even when they try to hold back their voice as
+they're being provoked, the sobs welling up from the
+back of their throat can't be stopped.</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -4294,8 +4298,8 @@
       </c>
       <c r="B251" s="1" t="inlineStr">
         <is>
-          <t>After she finishes counting, Rin-chan pulls her little
-finger away from the urethra.</t>
+          <t>After she finishes counting, Rin-chan pulls her
+little finger away from the urethra.</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -4370,7 +4374,8 @@
       </c>
       <c r="B256" s="1" t="inlineStr">
         <is>
-          <t>At that moment, semen erupted as if about to overflow.</t>
+          <t>At that moment, semen erupted as if about to
+overflow.</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -4416,8 +4421,8 @@
       </c>
       <c r="B259" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan is totally pleased with herself for making me
-cum...</t>
+          <t>Rin-chan is totally pleased with herself for making
+me cum...</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -5109,8 +5114,8 @@
       </c>
       <c r="B304" s="1" t="inlineStr">
         <is>
-          <t>Just like Rin-chan says, her pussy has already started
-moving with life.</t>
+          <t>Just like Rin-chan says, her pussy has already
+started moving with life.</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -5432,8 +5437,8 @@
       </c>
       <c r="B325" s="1" t="inlineStr">
         <is>
-          <t>「Rin, ri... nnh！ shuu, it's... so good, it's making me
-feel amazing！ Faaa！」</t>
+          <t>「Rin, ri... nnh！ shuu, it's... so good, it's making
+me feel amazing！ Faaa！」</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -5661,8 +5666,8 @@
       </c>
       <c r="B340" s="1" t="inlineStr">
         <is>
-          <t>Looking at that smile, I almost want to just stay like
-this...</t>
+          <t>Looking at that smile, I almost want to just stay
+like this...</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -5861,8 +5866,8 @@
       </c>
       <c r="B353" s="1" t="inlineStr">
         <is>
-          <t>Ohhh... maybe because she's drunk, she's saying things
-she'd never say when sober.</t>
+          <t>Ohhh... maybe because she's drunk, she's saying
+things she'd never say when sober.</t>
         </is>
       </c>
       <c r="C353" t="n">
@@ -6229,7 +6234,8 @@
       </c>
       <c r="B377" s="1" t="inlineStr">
         <is>
-          <t>So I pull my face away, but Rin-chan's lips follow me.</t>
+          <t>So I pull my face away, but Rin-chan's lips follow
+me.</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -6385,8 +6391,8 @@
       </c>
       <c r="B387" s="1" t="inlineStr">
         <is>
-          <t>Her small body is already fully formed, and it presses
-its warmth firmly against me.</t>
+          <t>Her small body is already fully formed, and it
+presses its warmth firmly against me.</t>
         </is>
       </c>
       <c r="C387" t="n">
@@ -6446,7 +6452,8 @@
       </c>
       <c r="B391" s="1" t="inlineStr">
         <is>
-          <t>「Ah... ha！ Ngh, chu...！ My pussy... squeezed, ahhh...」</t>
+          <t>「Ah... ha！ Ngh, chu...！ My pussy... squeezed,
+ahhh...」</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -6569,8 +6576,8 @@
       </c>
       <c r="B399" s="1" t="inlineStr">
         <is>
-          <t>「Rin-chan’s pussy… it’s sooooo, chu！ You’re getting so
-horny… n-chu chu！」</t>
+          <t>「Rin-chan’s pussy… it’s sooooo, chu！ You’re getting
+so horny… n-chu chu！」</t>
         </is>
       </c>
       <c r="C399" t="n">
@@ -7033,8 +7040,8 @@
       </c>
       <c r="B429" s="1" t="inlineStr">
         <is>
-          <t>Ah... having my face licked might not be so bad, after
-all...</t>
+          <t>Ah... having my face licked might not be so bad,
+after all...</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -7815,8 +7822,8 @@
       </c>
       <c r="B480" s="1" t="inlineStr">
         <is>
-          <t>But even that didn’t matter as we slipped into a world
-that belonged only to me and Rin-chan.</t>
+          <t>But even that didn’t matter as we slipped into a
+world that belonged only to me and Rin-chan.</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -7986,8 +7993,8 @@
       </c>
       <c r="B491" s="1" t="inlineStr">
         <is>
-          <t>A pleasant sensation reaches the tips of my toes, then
-flows back to my hips and converges on my penis.</t>
+          <t>A pleasant sensation reaches the tips of my toes,
+then flows back to my hips and converges on my penis.</t>
         </is>
       </c>
       <c r="C491" t="n">
@@ -8002,8 +8009,8 @@
       </c>
       <c r="B492" s="1" t="inlineStr">
         <is>
-          <t>Even so, because I want to be connected to Rin-chan in
-every way, I can't let our lips part.</t>
+          <t>Even so, because I want to be connected to Rin-chan
+in every way, I can't let our lips part.</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -8079,8 +8086,8 @@
       </c>
       <c r="B497" s="1" t="inlineStr">
         <is>
-          <t>While feeling an unavoidable urge to ejaculate, I suck
-hungrily on Rin-chan's lips.</t>
+          <t>While feeling an unavoidable urge to ejaculate, I
+suck hungrily on Rin-chan's lips.</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -8233,8 +8240,8 @@
       </c>
       <c r="B507" s="1" t="inlineStr">
         <is>
-          <t>Even though she's in the middle of coming, she doesn't
-stop kissing me or grinding her hips.</t>
+          <t>Even though she's in the middle of coming, she
+doesn't stop kissing me or grinding her hips.</t>
         </is>
       </c>
       <c r="C507" t="n">
@@ -8477,8 +8484,8 @@
       </c>
       <c r="B523" s="1" t="inlineStr">
         <is>
-          <t>Rin-chan’s pussy still moves, pulsing as if to squeeze
-my penis.</t>
+          <t>Rin-chan’s pussy still moves, pulsing as if to
+squeeze my penis.</t>
         </is>
       </c>
       <c r="C523" t="n">
@@ -8584,8 +8591,8 @@
       </c>
       <c r="B530" s="1" t="inlineStr">
         <is>
-          <t>Even though I was asleep, I kept coming, so I probably
-pushed myself too far.</t>
+          <t>Even though I was asleep, I kept coming, so I
+probably pushed myself too far.</t>
         </is>
       </c>
       <c r="C530" t="n">
@@ -8953,8 +8960,8 @@
       </c>
       <c r="B554" s="1" t="inlineStr">
         <is>
-          <t>As everyone woke up and started getting ready to clean
-up, Miru-chan let out a cheerful little voice.</t>
+          <t>As everyone woke up and started getting ready to
+clean up, Miru-chan let out a cheerful little voice.</t>
         </is>
       </c>
       <c r="C554" t="n">
@@ -9383,7 +9390,8 @@
       </c>
       <c r="B582" s="1" t="inlineStr">
         <is>
-          <t>Ugh... the dried cum from last night is stuck to it...</t>
+          <t>Ugh... the dried cum from last night is stuck to
+it...</t>
         </is>
       </c>
       <c r="C582" t="n">
@@ -10048,8 +10056,8 @@
       </c>
       <c r="B625" s="1" t="inlineStr">
         <is>
-          <t>「Oh my！ So, what kind of deduction will Oji-sama make？
-I'm excited...！」</t>
+          <t>「Oh my！ So, what kind of deduction will Oji-sama
+make？ I'm excited...！」</t>
         </is>
       </c>
       <c r="C625" t="n">
@@ -10140,8 +10148,8 @@
       </c>
       <c r="B631" s="1" t="inlineStr">
         <is>
-          <t>She's probably embarrassed, but I guess she'll need to
-reflect on this...！</t>
+          <t>She's probably embarrassed, but I guess she'll need
+to reflect on this...！</t>
         </is>
       </c>
       <c r="C631" t="n">
@@ -10172,8 +10180,8 @@
       <c r="B633" s="1" t="inlineStr">
         <is>
           <t>「First... this bedspread that got wet from bedwetting
-— the wet area is small, so it's not the amount of pee
-an adult would make...！」</t>
+— the wet area is small, so it's not the amount of
+pee an adult would make...！」</t>
         </is>
       </c>
       <c r="C633" t="n">
@@ -10236,8 +10244,8 @@
       </c>
       <c r="B637" s="1" t="inlineStr">
         <is>
-          <t>「However, in that case, I don't think the total amount
-matters much.」</t>
+          <t>「However, in that case, I don't think the total
+amount matters much.」</t>
         </is>
       </c>
       <c r="C637" t="n">
@@ -10451,8 +10459,8 @@
       </c>
       <c r="B651" s="1" t="inlineStr">
         <is>
-          <t>Thinking they'd poke holes in it again made my mind go
-blank.</t>
+          <t>Thinking they'd poke holes in it again made my mind
+go blank.</t>
         </is>
       </c>
       <c r="C651" t="n">
@@ -10651,8 +10659,8 @@
       </c>
       <c r="B664" s="1" t="inlineStr">
         <is>
-          <t>「And then... the whiskey bonbon that was in the snacks
-is gone！？」</t>
+          <t>「And then... the whiskey bonbon that was in the
+snacks is gone！？」</t>
         </is>
       </c>
       <c r="C664" t="n">
@@ -10727,8 +10735,8 @@
       </c>
       <c r="B669" s="1" t="inlineStr">
         <is>
-          <t>I turned to Rin-chan, making a big show of it, and the
-moment our eyes met she cracked and gave in.</t>
+          <t>I turned to Rin-chan, making a big show of it, and
+the moment our eyes met she cracked and gave in.</t>
         </is>
       </c>
       <c r="C669" t="n">
@@ -11047,8 +11055,8 @@
       </c>
       <c r="B690" s="1" t="inlineStr">
         <is>
-          <t>Everyone accused me one after another, and I let out a
-pathetic sound.</t>
+          <t>Everyone accused me one after another, and I let out
+a pathetic sound.</t>
         </is>
       </c>
       <c r="C690" t="n">

--- a/processed_ruby_restored_xlsx/sc235_凛７：天体観測.ss.xlsx
+++ b/processed_ruby_restored_xlsx/sc235_凛７：天体観測.ss.xlsx
@@ -697,7 +697,7 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>「Mmm—...？」</t>
+          <t>Mmm—...？</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1309,7 +1309,7 @@
       <c r="B56" s="1" t="inlineStr">
         <is>
           <t>Rin-chan loves teasing, but was she always this
-forward...?</t>
+forward...?"</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -2471,8 +2471,8 @@
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>Right at the moment my body jolted, I finally grabbed
-the tip of my penis.</t>
+          <t>Right at the moment my body jolted, he finally
+grabbed the tip of my penis.</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>「Ah, nngh？ Eh, eh！？ S-that's not fair...」</t>
+          <t>Ah, nngh？ Eh, eh！？ S-that's not fair...</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="B242" s="1" t="inlineStr">
         <is>
-          <t>「Nii~...！ A little more... just a liiiittle more...！」</t>
+          <t>Nii~...！ A little more... just a liiiittle more...！</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="B254" s="1" t="inlineStr">
         <is>
-          <t>「Nnnggh~ faaah mmmfwah~！」</t>
+          <t>Nnnggh~ faaah mmmfwah~！</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -4944,8 +4944,8 @@
       </c>
       <c r="B293" s="1" t="inlineStr">
         <is>
-          <t>Before I even have a moment to savor the afterglow of
-ejaculation, my penis is once again wrapped in
+          <t>Before he even has a moment to savor the afterglow of
+ejaculation, his penis is once again wrapped in
 pleasure.</t>
         </is>
       </c>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="B380" s="1" t="inlineStr">
         <is>
-          <t>「chu-puu... gyuu！ gyuuu...！」</t>
+          <t>chu-puu... gyuu！ gyuuu...！</t>
         </is>
       </c>
       <c r="C380" t="n">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="B389" s="1" t="inlineStr">
         <is>
-          <t>「Chup…！ Haa, faa… Kohhi, mooo… gyu, gyuuuh… tte！」</t>
+          <t>Chup…！ Haa, faa… Kohhi, mooo… gyu, gyuuuh… tte！</t>
         </is>
       </c>
       <c r="C389" t="n">
@@ -6514,8 +6514,8 @@
       </c>
       <c r="B395" s="1" t="inlineStr">
         <is>
-          <t>And then if her face moves away even a little, she
-immediately goes for another kiss — it’s so cute….</t>
+          <t>And then if their face moves away even a little, they
+immediately go for another kiss — it’s so cute….</t>
         </is>
       </c>
       <c r="C395" t="n">
@@ -6545,8 +6545,7 @@
       </c>
       <c r="B397" s="1" t="inlineStr">
         <is>
-          <t>「Ahn... smooch！ Fwaaah... all melty... smoooch...
-nfu！」</t>
+          <t>Ahn... smooch！ Fwaaah... all melty... smoooch... nfu！</t>
         </is>
       </c>
       <c r="C397" t="n">
@@ -6840,7 +6839,7 @@
       </c>
       <c r="B416" s="1" t="inlineStr">
         <is>
-          <t>Rin</t>
+          <t>Rin-chan</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -6886,7 +6885,7 @@
       </c>
       <c r="B419" s="1" t="inlineStr">
         <is>
-          <t>Rin</t>
+          <t>Rin-chan</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -7024,8 +7023,8 @@
       </c>
       <c r="B428" s="1" t="inlineStr">
         <is>
-          <t>「Auuuun... prrr！ Lero, leroo... smooch！ Wauau！ Lero,
-smooch, smooooch...」</t>
+          <t>Auuuun... prrr！ Lero, leroo... smooch！ Wauau！ Lero,
+smooch, smooooch...</t>
         </is>
       </c>
       <c r="C428" t="n">
@@ -7178,7 +7177,7 @@
       </c>
       <c r="B438" s="1" t="inlineStr">
         <is>
-          <t>「Aahf！ Wauuu… chu, lero！ lero！ chupa！ ero-lero！」</t>
+          <t>Aahf！ Wauuu… chu, lero！ lero！ chupa！ ero-lero！</t>
         </is>
       </c>
       <c r="C438" t="n">
@@ -7193,8 +7192,8 @@
       </c>
       <c r="B439" s="1" t="inlineStr">
         <is>
-          <t>She licks my lips, then gives the tip of my nose a
-lick. Then she goes over my cheeks, my ears, even the
+          <t>They lick my lips, then give the tip of my nose a
+lick. Then they go over my cheeks, my ears, even the
 hollows by my eyes, thoroughly licking me all over.</t>
         </is>
       </c>
@@ -7270,7 +7269,7 @@
       </c>
       <c r="B444" s="1" t="inlineStr">
         <is>
-          <t>「I'll make you feel really good, okay？」</t>
+          <t>I'll make you feel really good, okay？</t>
         </is>
       </c>
       <c r="C444" t="n">
@@ -7577,7 +7576,7 @@
       </c>
       <c r="B464" s="1" t="inlineStr">
         <is>
-          <t>「Nn... ah—！」</t>
+          <t>Nn... ah—！</t>
         </is>
       </c>
       <c r="C464" t="n">
@@ -7698,7 +7697,7 @@
       </c>
       <c r="B472" s="1" t="inlineStr">
         <is>
-          <t>I probably figured that the one kissing could get by
+          <t>He probably figured that the one kissing could get by
 without having to shout.</t>
         </is>
       </c>
@@ -7729,7 +7728,7 @@
       </c>
       <c r="B474" s="1" t="inlineStr">
         <is>
-          <t>「Smooch... chu-chu, chuuu... schmoooch！」</t>
+          <t>Smooch... chu-chu, chuuu... schmoooch！</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -8040,8 +8039,8 @@
       </c>
       <c r="B494" s="1" t="inlineStr">
         <is>
-          <t>「Smooch！ Smoooch... Smooch！ Aaah, nnngh！ Smooo...
-Smpf！ Chup-chup-paah！」</t>
+          <t>Smooch！ Smoooch... Smooch！ Aaah, nnngh！ Smooo...
+Smpf！ Chup-chup-paah！</t>
         </is>
       </c>
       <c r="C494" t="n">
@@ -8424,7 +8423,7 @@
       </c>
       <c r="B519" s="1" t="inlineStr">
         <is>
-          <t>「Mmm—！ Nnchu, ahh... ah！ It's still... coming！」</t>
+          <t>Mmm—！ Nnchu, ahh... ah！ It's still... coming！</t>
         </is>
       </c>
       <c r="C519" t="n">
@@ -8469,7 +8468,7 @@
       </c>
       <c r="B522" s="1" t="inlineStr">
         <is>
-          <t>「Nnnh！ Nnh, again—keep cumming, uuuh！」</t>
+          <t>Nnnh！ Nnh, again—keep cumming, uuuh！</t>
         </is>
       </c>
       <c r="C522" t="n">
@@ -8485,7 +8484,7 @@
       <c r="B523" s="1" t="inlineStr">
         <is>
           <t>Rin-chan’s pussy still moves, pulsing as if to
-squeeze my penis.</t>
+squeeze his penis.</t>
         </is>
       </c>
       <c r="C523" t="n">
@@ -8575,7 +8574,7 @@
       </c>
       <c r="B529" s="1" t="inlineStr">
         <is>
-          <t>In the end, exhaustion finally hits and my hips go
+          <t>In the end, exhaustion finally hits and his hips go
 slack.</t>
         </is>
       </c>
@@ -9112,7 +9111,7 @@
       </c>
       <c r="B564" s="1" t="inlineStr">
         <is>
-          <t>「W-well...」</t>
+          <t>W-well...</t>
         </is>
       </c>
       <c r="C564" t="n">
@@ -10308,7 +10307,7 @@
         <is>
           <t>I see... because we don't know how much soaked into
 the underwear, we didn't need to argue about the
-amount...！？</t>
+amount...！？"</t>
         </is>
       </c>
       <c r="C641" t="n">
